--- a/qa-suites/ui-ux-test-report.xlsx
+++ b/qa-suites/ui-ux-test-report.xlsx
@@ -32,7 +32,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>24/7/2026, 6:38:01 pm</t>
+    <t>24/7/2026, 7:24:50 pm</t>
   </si>
   <si>
     <t>Deployment Status</t>
@@ -2225,7 +2225,7 @@
         <v>38</v>
       </c>
       <c r="K2" s="7">
-        <v>384</v>
+        <v>55</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>15</v>
@@ -2263,7 +2263,7 @@
         <v>43</v>
       </c>
       <c r="K3" s="9">
-        <v>220</v>
+        <v>291</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>15</v>
@@ -2301,7 +2301,7 @@
         <v>48</v>
       </c>
       <c r="K4" s="7">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>15</v>
@@ -2339,7 +2339,7 @@
         <v>38</v>
       </c>
       <c r="K5" s="9">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>15</v>
@@ -2377,7 +2377,7 @@
         <v>43</v>
       </c>
       <c r="K6" s="7">
-        <v>32</v>
+        <v>341</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>15</v>
@@ -2415,7 +2415,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="9">
-        <v>442</v>
+        <v>152</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>15</v>
@@ -2453,7 +2453,7 @@
         <v>38</v>
       </c>
       <c r="K8" s="7">
-        <v>144</v>
+        <v>400</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>15</v>
@@ -2491,7 +2491,7 @@
         <v>43</v>
       </c>
       <c r="K9" s="9">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>15</v>
@@ -2529,7 +2529,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="7">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>15</v>
@@ -2567,7 +2567,7 @@
         <v>38</v>
       </c>
       <c r="K11" s="9">
-        <v>231</v>
+        <v>56</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>15</v>
@@ -2605,7 +2605,7 @@
         <v>43</v>
       </c>
       <c r="K12" s="7">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>15</v>
@@ -2643,7 +2643,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="9">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>15</v>
@@ -2681,7 +2681,7 @@
         <v>38</v>
       </c>
       <c r="K14" s="7">
-        <v>49</v>
+        <v>313</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>15</v>
@@ -2719,7 +2719,7 @@
         <v>43</v>
       </c>
       <c r="K15" s="9">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>15</v>
@@ -2757,7 +2757,7 @@
         <v>48</v>
       </c>
       <c r="K16" s="7">
-        <v>469</v>
+        <v>277</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>15</v>
@@ -2795,7 +2795,7 @@
         <v>38</v>
       </c>
       <c r="K17" s="9">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>15</v>
@@ -2833,7 +2833,7 @@
         <v>43</v>
       </c>
       <c r="K18" s="7">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>15</v>
@@ -2871,7 +2871,7 @@
         <v>48</v>
       </c>
       <c r="K19" s="9">
-        <v>65</v>
+        <v>332</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>15</v>
@@ -2909,7 +2909,7 @@
         <v>38</v>
       </c>
       <c r="K20" s="7">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>15</v>
@@ -2947,7 +2947,7 @@
         <v>43</v>
       </c>
       <c r="K21" s="9">
-        <v>411</v>
+        <v>293</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>15</v>
@@ -2985,7 +2985,7 @@
         <v>48</v>
       </c>
       <c r="K22" s="7">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>15</v>
@@ -3023,7 +3023,7 @@
         <v>38</v>
       </c>
       <c r="K23" s="9">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>15</v>
@@ -3061,7 +3061,7 @@
         <v>43</v>
       </c>
       <c r="K24" s="7">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>15</v>
@@ -3099,7 +3099,7 @@
         <v>48</v>
       </c>
       <c r="K25" s="9">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>15</v>
@@ -3137,7 +3137,7 @@
         <v>38</v>
       </c>
       <c r="K26" s="7">
-        <v>87</v>
+        <v>388</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>15</v>
@@ -3175,7 +3175,7 @@
         <v>43</v>
       </c>
       <c r="K27" s="9">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>15</v>
@@ -3213,7 +3213,7 @@
         <v>48</v>
       </c>
       <c r="K28" s="7">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>15</v>
@@ -3251,7 +3251,7 @@
         <v>38</v>
       </c>
       <c r="K29" s="9">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>15</v>
@@ -3289,7 +3289,7 @@
         <v>43</v>
       </c>
       <c r="K30" s="7">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>15</v>
@@ -3327,7 +3327,7 @@
         <v>48</v>
       </c>
       <c r="K31" s="9">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>15</v>
@@ -3365,7 +3365,7 @@
         <v>38</v>
       </c>
       <c r="K32" s="7">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>15</v>
@@ -3403,7 +3403,7 @@
         <v>43</v>
       </c>
       <c r="K33" s="9">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>15</v>
@@ -3441,7 +3441,7 @@
         <v>48</v>
       </c>
       <c r="K34" s="7">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>15</v>
@@ -3479,7 +3479,7 @@
         <v>38</v>
       </c>
       <c r="K35" s="9">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>15</v>
@@ -3517,7 +3517,7 @@
         <v>43</v>
       </c>
       <c r="K36" s="7">
-        <v>178</v>
+        <v>455</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>15</v>
@@ -3555,7 +3555,7 @@
         <v>48</v>
       </c>
       <c r="K37" s="9">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>15</v>
@@ -3593,7 +3593,7 @@
         <v>38</v>
       </c>
       <c r="K38" s="7">
-        <v>403</v>
+        <v>235</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>153</v>
@@ -3631,7 +3631,7 @@
         <v>43</v>
       </c>
       <c r="K39" s="9">
-        <v>466</v>
+        <v>121</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>15</v>
@@ -3669,7 +3669,7 @@
         <v>48</v>
       </c>
       <c r="K40" s="7">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>15</v>
@@ -3707,7 +3707,7 @@
         <v>38</v>
       </c>
       <c r="K41" s="9">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>15</v>
@@ -3745,7 +3745,7 @@
         <v>43</v>
       </c>
       <c r="K42" s="7">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>15</v>
@@ -3783,7 +3783,7 @@
         <v>48</v>
       </c>
       <c r="K43" s="9">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>15</v>
@@ -3821,7 +3821,7 @@
         <v>38</v>
       </c>
       <c r="K44" s="7">
-        <v>390</v>
+        <v>185</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>15</v>
@@ -3859,7 +3859,7 @@
         <v>43</v>
       </c>
       <c r="K45" s="9">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>15</v>
@@ -3897,7 +3897,7 @@
         <v>48</v>
       </c>
       <c r="K46" s="7">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>15</v>
@@ -3935,7 +3935,7 @@
         <v>38</v>
       </c>
       <c r="K47" s="9">
-        <v>87</v>
+        <v>387</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>15</v>
@@ -3973,7 +3973,7 @@
         <v>43</v>
       </c>
       <c r="K48" s="7">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>15</v>
@@ -4011,7 +4011,7 @@
         <v>48</v>
       </c>
       <c r="K49" s="9">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>15</v>
@@ -4049,7 +4049,7 @@
         <v>38</v>
       </c>
       <c r="K50" s="7">
-        <v>231</v>
+        <v>450</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>15</v>
@@ -4087,7 +4087,7 @@
         <v>43</v>
       </c>
       <c r="K51" s="9">
-        <v>32</v>
+        <v>299</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>15</v>
@@ -4125,7 +4125,7 @@
         <v>48</v>
       </c>
       <c r="K52" s="7">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>15</v>
@@ -4163,7 +4163,7 @@
         <v>38</v>
       </c>
       <c r="K53" s="9">
-        <v>29</v>
+        <v>409</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>15</v>
@@ -4201,7 +4201,7 @@
         <v>43</v>
       </c>
       <c r="K54" s="7">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>15</v>
@@ -4239,7 +4239,7 @@
         <v>48</v>
       </c>
       <c r="K55" s="9">
-        <v>423</v>
+        <v>76</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>15</v>
@@ -4277,7 +4277,7 @@
         <v>38</v>
       </c>
       <c r="K56" s="7">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>15</v>
@@ -4315,7 +4315,7 @@
         <v>43</v>
       </c>
       <c r="K57" s="9">
-        <v>395</v>
+        <v>27</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>15</v>
@@ -4353,7 +4353,7 @@
         <v>48</v>
       </c>
       <c r="K58" s="7">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>15</v>
@@ -4391,7 +4391,7 @@
         <v>38</v>
       </c>
       <c r="K59" s="9">
-        <v>387</v>
+        <v>185</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>15</v>
@@ -4429,7 +4429,7 @@
         <v>43</v>
       </c>
       <c r="K60" s="7">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>15</v>
@@ -4467,7 +4467,7 @@
         <v>48</v>
       </c>
       <c r="K61" s="9">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>15</v>
@@ -4505,7 +4505,7 @@
         <v>38</v>
       </c>
       <c r="K62" s="7">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>15</v>
@@ -4543,7 +4543,7 @@
         <v>43</v>
       </c>
       <c r="K63" s="9">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>15</v>
@@ -4581,7 +4581,7 @@
         <v>48</v>
       </c>
       <c r="K64" s="7">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>15</v>
@@ -4619,7 +4619,7 @@
         <v>38</v>
       </c>
       <c r="K65" s="9">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>15</v>
@@ -4657,7 +4657,7 @@
         <v>43</v>
       </c>
       <c r="K66" s="7">
-        <v>295</v>
+        <v>388</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>15</v>
@@ -4695,7 +4695,7 @@
         <v>48</v>
       </c>
       <c r="K67" s="9">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>15</v>
@@ -4733,7 +4733,7 @@
         <v>38</v>
       </c>
       <c r="K68" s="7">
-        <v>225</v>
+        <v>447</v>
       </c>
       <c r="L68" s="11" t="s">
         <v>244</v>
@@ -4771,7 +4771,7 @@
         <v>43</v>
       </c>
       <c r="K69" s="9">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>15</v>
@@ -4809,7 +4809,7 @@
         <v>48</v>
       </c>
       <c r="K70" s="7">
-        <v>464</v>
+        <v>110</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>15</v>
@@ -4847,7 +4847,7 @@
         <v>38</v>
       </c>
       <c r="K71" s="9">
-        <v>397</v>
+        <v>458</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>15</v>
@@ -4885,7 +4885,7 @@
         <v>43</v>
       </c>
       <c r="K72" s="7">
-        <v>331</v>
+        <v>200</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>15</v>
@@ -4923,7 +4923,7 @@
         <v>48</v>
       </c>
       <c r="K73" s="9">
-        <v>400</v>
+        <v>141</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>15</v>
@@ -4961,7 +4961,7 @@
         <v>38</v>
       </c>
       <c r="K74" s="7">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>15</v>
@@ -4999,7 +4999,7 @@
         <v>43</v>
       </c>
       <c r="K75" s="9">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="L75" s="10" t="s">
         <v>153</v>
@@ -5037,7 +5037,7 @@
         <v>48</v>
       </c>
       <c r="K76" s="7">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>15</v>
@@ -5075,7 +5075,7 @@
         <v>38</v>
       </c>
       <c r="K77" s="9">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>15</v>
@@ -5113,7 +5113,7 @@
         <v>43</v>
       </c>
       <c r="K78" s="7">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>15</v>
@@ -5151,7 +5151,7 @@
         <v>48</v>
       </c>
       <c r="K79" s="9">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>15</v>
@@ -5189,7 +5189,7 @@
         <v>38</v>
       </c>
       <c r="K80" s="7">
-        <v>435</v>
+        <v>342</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>15</v>
@@ -5227,7 +5227,7 @@
         <v>43</v>
       </c>
       <c r="K81" s="9">
-        <v>428</v>
+        <v>308</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>15</v>
@@ -5265,7 +5265,7 @@
         <v>48</v>
       </c>
       <c r="K82" s="7">
-        <v>22</v>
+        <v>257</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>15</v>
@@ -5303,7 +5303,7 @@
         <v>38</v>
       </c>
       <c r="K83" s="9">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>15</v>
@@ -5341,7 +5341,7 @@
         <v>43</v>
       </c>
       <c r="K84" s="7">
-        <v>271</v>
+        <v>401</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>15</v>
@@ -5379,7 +5379,7 @@
         <v>48</v>
       </c>
       <c r="K85" s="9">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>15</v>
@@ -5417,7 +5417,7 @@
         <v>38</v>
       </c>
       <c r="K86" s="7">
-        <v>409</v>
+        <v>100</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>15</v>
@@ -5455,7 +5455,7 @@
         <v>43</v>
       </c>
       <c r="K87" s="9">
-        <v>116</v>
+        <v>282</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>15</v>
@@ -5493,7 +5493,7 @@
         <v>48</v>
       </c>
       <c r="K88" s="7">
-        <v>468</v>
+        <v>129</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>15</v>
@@ -5531,7 +5531,7 @@
         <v>38</v>
       </c>
       <c r="K89" s="9">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>15</v>
@@ -5569,7 +5569,7 @@
         <v>43</v>
       </c>
       <c r="K90" s="7">
-        <v>266</v>
+        <v>438</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>15</v>
@@ -5607,7 +5607,7 @@
         <v>48</v>
       </c>
       <c r="K91" s="9">
-        <v>461</v>
+        <v>56</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>15</v>
@@ -5645,7 +5645,7 @@
         <v>38</v>
       </c>
       <c r="K92" s="7">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>15</v>
@@ -5683,7 +5683,7 @@
         <v>43</v>
       </c>
       <c r="K93" s="9">
-        <v>236</v>
+        <v>402</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>15</v>
@@ -5721,7 +5721,7 @@
         <v>48</v>
       </c>
       <c r="K94" s="7">
-        <v>293</v>
+        <v>38</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>15</v>
@@ -5759,7 +5759,7 @@
         <v>38</v>
       </c>
       <c r="K95" s="9">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>15</v>
@@ -5797,7 +5797,7 @@
         <v>43</v>
       </c>
       <c r="K96" s="7">
-        <v>125</v>
+        <v>317</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>15</v>
@@ -5835,7 +5835,7 @@
         <v>48</v>
       </c>
       <c r="K97" s="9">
-        <v>422</v>
+        <v>210</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>15</v>
@@ -5873,7 +5873,7 @@
         <v>38</v>
       </c>
       <c r="K98" s="7">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>15</v>
@@ -5911,7 +5911,7 @@
         <v>43</v>
       </c>
       <c r="K99" s="9">
-        <v>304</v>
+        <v>462</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>15</v>
@@ -5949,7 +5949,7 @@
         <v>48</v>
       </c>
       <c r="K100" s="7">
-        <v>386</v>
+        <v>176</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>15</v>
@@ -5987,7 +5987,7 @@
         <v>38</v>
       </c>
       <c r="K101" s="9">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>15</v>
@@ -6025,7 +6025,7 @@
         <v>43</v>
       </c>
       <c r="K102" s="7">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>15</v>
@@ -6063,7 +6063,7 @@
         <v>48</v>
       </c>
       <c r="K103" s="9">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>15</v>
@@ -6101,7 +6101,7 @@
         <v>38</v>
       </c>
       <c r="K104" s="7">
-        <v>298</v>
+        <v>67</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>15</v>
@@ -6139,7 +6139,7 @@
         <v>43</v>
       </c>
       <c r="K105" s="9">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>15</v>
@@ -6177,7 +6177,7 @@
         <v>48</v>
       </c>
       <c r="K106" s="7">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>15</v>
@@ -6215,7 +6215,7 @@
         <v>38</v>
       </c>
       <c r="K107" s="9">
-        <v>85</v>
+        <v>444</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>15</v>
@@ -6253,7 +6253,7 @@
         <v>43</v>
       </c>
       <c r="K108" s="7">
-        <v>319</v>
+        <v>101</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>15</v>
@@ -6291,7 +6291,7 @@
         <v>48</v>
       </c>
       <c r="K109" s="9">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>15</v>
@@ -6329,7 +6329,7 @@
         <v>38</v>
       </c>
       <c r="K110" s="7">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>15</v>
@@ -6367,7 +6367,7 @@
         <v>43</v>
       </c>
       <c r="K111" s="9">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>15</v>
@@ -6405,7 +6405,7 @@
         <v>48</v>
       </c>
       <c r="K112" s="7">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="L112" s="10" t="s">
         <v>153</v>
@@ -6443,7 +6443,7 @@
         <v>38</v>
       </c>
       <c r="K113" s="9">
-        <v>228</v>
+        <v>317</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>15</v>
@@ -6481,7 +6481,7 @@
         <v>43</v>
       </c>
       <c r="K114" s="7">
-        <v>267</v>
+        <v>148</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>15</v>
@@ -6519,7 +6519,7 @@
         <v>48</v>
       </c>
       <c r="K115" s="9">
-        <v>312</v>
+        <v>56</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>15</v>
@@ -6557,7 +6557,7 @@
         <v>38</v>
       </c>
       <c r="K116" s="7">
-        <v>383</v>
+        <v>264</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>15</v>
@@ -6595,7 +6595,7 @@
         <v>43</v>
       </c>
       <c r="K117" s="9">
-        <v>161</v>
+        <v>422</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>15</v>
@@ -6633,7 +6633,7 @@
         <v>48</v>
       </c>
       <c r="K118" s="7">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>15</v>
@@ -6671,7 +6671,7 @@
         <v>38</v>
       </c>
       <c r="K119" s="9">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>15</v>
@@ -6709,7 +6709,7 @@
         <v>43</v>
       </c>
       <c r="K120" s="7">
-        <v>271</v>
+        <v>28</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>15</v>
@@ -6747,7 +6747,7 @@
         <v>48</v>
       </c>
       <c r="K121" s="9">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>15</v>
@@ -6785,7 +6785,7 @@
         <v>38</v>
       </c>
       <c r="K122" s="7">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>15</v>
@@ -6823,7 +6823,7 @@
         <v>43</v>
       </c>
       <c r="K123" s="9">
-        <v>299</v>
+        <v>220</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>15</v>
@@ -6861,7 +6861,7 @@
         <v>48</v>
       </c>
       <c r="K124" s="7">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>15</v>
@@ -6899,7 +6899,7 @@
         <v>38</v>
       </c>
       <c r="K125" s="9">
-        <v>317</v>
+        <v>34</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>15</v>
@@ -6937,7 +6937,7 @@
         <v>43</v>
       </c>
       <c r="K126" s="7">
-        <v>226</v>
+        <v>382</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>15</v>
@@ -6975,7 +6975,7 @@
         <v>48</v>
       </c>
       <c r="K127" s="9">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>15</v>
@@ -7013,7 +7013,7 @@
         <v>38</v>
       </c>
       <c r="K128" s="7">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>15</v>
@@ -7051,7 +7051,7 @@
         <v>43</v>
       </c>
       <c r="K129" s="9">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>15</v>
@@ -7089,7 +7089,7 @@
         <v>48</v>
       </c>
       <c r="K130" s="7">
-        <v>384</v>
+        <v>46</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>38</v>
       </c>
       <c r="K131" s="9">
-        <v>407</v>
+        <v>172</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>15</v>
@@ -7165,7 +7165,7 @@
         <v>43</v>
       </c>
       <c r="K132" s="7">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>15</v>
@@ -7203,7 +7203,7 @@
         <v>48</v>
       </c>
       <c r="K133" s="9">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>15</v>
@@ -7241,7 +7241,7 @@
         <v>38</v>
       </c>
       <c r="K134" s="7">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>15</v>
@@ -7279,7 +7279,7 @@
         <v>43</v>
       </c>
       <c r="K135" s="9">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="L135" s="11" t="s">
         <v>244</v>
@@ -7317,7 +7317,7 @@
         <v>48</v>
       </c>
       <c r="K136" s="7">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>15</v>
@@ -7355,7 +7355,7 @@
         <v>38</v>
       </c>
       <c r="K137" s="9">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="L137" s="8" t="s">
         <v>15</v>
@@ -7393,7 +7393,7 @@
         <v>43</v>
       </c>
       <c r="K138" s="7">
-        <v>291</v>
+        <v>455</v>
       </c>
       <c r="L138" s="8" t="s">
         <v>15</v>
@@ -7431,7 +7431,7 @@
         <v>48</v>
       </c>
       <c r="K139" s="9">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>15</v>
@@ -7469,7 +7469,7 @@
         <v>38</v>
       </c>
       <c r="K140" s="7">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>15</v>
@@ -7507,7 +7507,7 @@
         <v>43</v>
       </c>
       <c r="K141" s="9">
-        <v>455</v>
+        <v>181</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>15</v>
@@ -7545,7 +7545,7 @@
         <v>48</v>
       </c>
       <c r="K142" s="7">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>15</v>
@@ -7583,7 +7583,7 @@
         <v>38</v>
       </c>
       <c r="K143" s="9">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>15</v>
@@ -7621,7 +7621,7 @@
         <v>43</v>
       </c>
       <c r="K144" s="7">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>15</v>
@@ -7659,7 +7659,7 @@
         <v>48</v>
       </c>
       <c r="K145" s="9">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>15</v>
@@ -7697,7 +7697,7 @@
         <v>38</v>
       </c>
       <c r="K146" s="7">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>43</v>
       </c>
       <c r="K147" s="9">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="L147" s="8" t="s">
         <v>15</v>
@@ -7773,7 +7773,7 @@
         <v>48</v>
       </c>
       <c r="K148" s="7">
-        <v>440</v>
+        <v>332</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>15</v>
@@ -7811,7 +7811,7 @@
         <v>38</v>
       </c>
       <c r="K149" s="9">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="L149" s="10" t="s">
         <v>153</v>
@@ -7849,7 +7849,7 @@
         <v>43</v>
       </c>
       <c r="K150" s="7">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>15</v>
@@ -7887,7 +7887,7 @@
         <v>48</v>
       </c>
       <c r="K151" s="9">
-        <v>118</v>
+        <v>469</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>15</v>
